--- a/GENERATED/StructureDefinition-Etniatexto.xlsx
+++ b/GENERATED/StructureDefinition-Etniatexto.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-11T16:48:21-03:00</t>
+    <t>2023-01-11T19:25:19-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
